--- a/TestcaseCollection/002.xlsx
+++ b/TestcaseCollection/002.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>*用例编号</t>
   </si>
@@ -76,7 +76,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>AT092_001_001_015</t>
+    <t>AT092_001_001_016</t>
   </si>
   <si>
     <t>整车状态判断</t>
@@ -88,7 +88,7 @@
     <t>测试用例</t>
   </si>
   <si>
-    <t>OFF档</t>
+    <t>OK档</t>
   </si>
   <si>
     <t>点检功能测试/基础功能测试/全功能测试</t>
@@ -103,7 +103,7 @@
     <t>状态</t>
   </si>
   <si>
-    <t>测试台CAN输出(12D.BCMPower_Gear_12D_S,1);</t>
+    <t>测试台CAN输出(12D.BCMPower_Gear_12D_S,3);</t>
   </si>
   <si>
     <t>动作</t>
@@ -115,88 +115,7 @@
     <t>响应</t>
   </si>
   <si>
-    <t>HUD屏不亮</t>
-  </si>
-  <si>
-    <t>AT092_001_001_016</t>
-  </si>
-  <si>
-    <t>OK档</t>
-  </si>
-  <si>
-    <t>测试台CAN输出(12D.BCMPower_Gear_12D_S,3);</t>
-  </si>
-  <si>
     <t>HUD屏亮</t>
-  </si>
-  <si>
-    <t>AT092_001_001_026</t>
-  </si>
-  <si>
-    <t>HUD基础功能</t>
-  </si>
-  <si>
-    <t>主题切换</t>
-  </si>
-  <si>
-    <t>雪地模式</t>
-  </si>
-  <si>
-    <t>ON档电</t>
-  </si>
-  <si>
-    <t>收到PAD的"HUD主题模式"为雪地模式</t>
-  </si>
-  <si>
-    <t>测试台CAN输出(4C1.HUD_Mode_Settings_S,2);
-等待(50);</t>
-  </si>
-  <si>
-    <t>记忆主题设置为雪地模式，图标变成蓝色</t>
-  </si>
-  <si>
-    <t>测试台CAN采集(38B.HUD_Mode_Feedback_S,2);
-条件脚本求或(OR.1-1,TrueDo1-1,FalseDo2-7);
-等待(50);
-测试台CAN输出(4C1.HUD_Mode_Settings_S,1);
-等待(50);
-测试台CAN采集(38B.HUD_Mode_Feedback_S,2);
-条件脚本求或(OR.1-1,TrueDo1-1,FalseDo2-3);
-打印失败原因(HUD主题做反了);
-打印失败原因(HUD开关开启雪地模式);
-测试台CAN采集(38B.HUD_Mode_Feedback_S,2);</t>
-  </si>
-  <si>
-    <t>AT092_001_001_067</t>
-  </si>
-  <si>
-    <t>亮度档位调节</t>
-  </si>
-  <si>
-    <t>6档亮度</t>
-  </si>
-  <si>
-    <t>全功能测试</t>
-  </si>
-  <si>
-    <t>台架</t>
-  </si>
-  <si>
-    <t>等待(200);</t>
-  </si>
-  <si>
-    <t>PAD发送的"亮度档位设置"6档</t>
-  </si>
-  <si>
-    <t>测试台CAN输出(4C1.Media_Brightness_Set_S,6);</t>
-  </si>
-  <si>
-    <t>HUD亮度调整至6档，亮度发生变化</t>
-  </si>
-  <si>
-    <t>等待(200);
-测试台CAN采集(301.Brightness_Feedback_301_S,6);
-测试台CAN采集(38B.Brightness_Feedback_S,6);</t>
   </si>
 </sst>
 </file>
@@ -575,7 +494,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -587,19 +506,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -735,7 +641,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -747,34 +653,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -859,14 +765,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -874,9 +777,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1189,8 +1089,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1206,455 +1106,149 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:15">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" customHeight="1" spans="1:15">
-      <c r="A2" s="4" t="s">
+    <row r="2" s="1" customFormat="1" ht="27" spans="1:15">
+      <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4" t="s">
+      <c r="M2" s="3"/>
+      <c r="N2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="4"/>
+      <c r="O2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="81" spans="1:15">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="27" spans="1:15">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="27" spans="1:15">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+    <row r="4" s="1" customFormat="1" spans="1:15">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="27" spans="1:15">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:15">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="67.5" spans="1:15">
-      <c r="A6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="81" spans="1:15">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="27" spans="1:15">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:15">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="67.5" spans="1:16">
-      <c r="A10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="5"/>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="81" spans="1:16">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="5"/>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="108" spans="1:16">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="5"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="216" spans="1:16">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="5"/>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="27" spans="1:15">
-      <c r="A14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="O14" s="4"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:15">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="27" spans="1:15">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="67.5" spans="1:15">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
